--- a/output/2026-09-01_03_Italia_Umbria_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-01_03_Italia_Umbria_Depolverazione_Trattamento_aria.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Telefono ed email confermati da fonte indipendente (sihappy.it).</t>
+          <t>Telefono ed email confermati da fonte indipendente (sihappy.it). [DUPLICATO — vedi anche: 2026-08-31_09_Italia_Toscana_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -642,7 +642,6 @@
           <t>G.F. Industrial Services Italia S.r.l.s.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Perugia (PG) - Bastia Umbra</t>
@@ -653,8 +652,6 @@
           <t>Commercio all'ingrosso macchinari per verniciatura, aspirazione e trattamento aria per uso industriale (agenzia/rappresentanza commerciale, ATECO 46.62.00)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Esistenza confermata da registro imprese (P.IVA 03849950542). Nessun sito/telefono/email pubblico reperito: recuperare recapiti via CCIAA/PEC.</t>
